--- a/Source Data/Source_Data_Fig1.xlsx
+++ b/Source Data/Source_Data_Fig1.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samokeeffe/Documents/GitHub/abs-met-quant/Source Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3E5D88-8D56-D54D-B645-206E4A6CA879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AF91F8-CE17-274F-9CD2-8A07C89F937D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16300" xr2:uid="{AA3827AF-446B-C24D-8707-597C10DC6DC5}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16280" xr2:uid="{AA3827AF-446B-C24D-8707-597C10DC6DC5}"/>
   </bookViews>
   <sheets>
-    <sheet name="1f" sheetId="1" r:id="rId1"/>
+    <sheet name="1F" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
